--- a/faker/marketing_campaigns.xlsx
+++ b/faker/marketing_campaigns.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-08-04 22:17:04</t>
+          <t>2025-08-05 11:30:01</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-01-08 12:18:06</t>
+          <t>2026-01-09 01:31:03</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2025-07-22 06:42:43</t>
+          <t>2025-07-22 19:55:40</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>2025-10-07 22:30:01</t>
+          <t>2025-10-08 11:42:58</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>2025-01-29 06:43:56</t>
+          <t>2025-01-29 19:56:53</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>2025-04-02 02:16:46</t>
+          <t>2025-04-02 15:29:43</t>
         </is>
       </c>
     </row>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>2025-10-27 15:25:07</t>
+          <t>2025-10-28 04:38:04</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>2025-07-16 17:22:47</t>
+          <t>2025-07-17 06:35:44</t>
         </is>
       </c>
     </row>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>2025-01-13 09:10:51</t>
+          <t>2025-01-13 22:23:48</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23055,7 @@
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>2026-01-05 00:28:49</t>
+          <t>2026-01-05 13:41:46</t>
         </is>
       </c>
     </row>
@@ -23831,7 +23831,7 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2025-03-31 07:38:48  </t>
+          <t xml:space="preserve">  2025-03-31 20:51:45  </t>
         </is>
       </c>
     </row>
@@ -25155,7 +25155,7 @@
       </c>
       <c r="T321" t="inlineStr">
         <is>
-          <t>2025-03-08 02:48:31</t>
+          <t>2025-03-08 16:01:28</t>
         </is>
       </c>
     </row>
@@ -35818,7 +35818,7 @@
       </c>
       <c r="T460" t="inlineStr">
         <is>
-          <t>2025-07-17 12:42:43</t>
+          <t>2025-07-18 01:55:40</t>
         </is>
       </c>
     </row>

--- a/faker/marketing_campaigns.xlsx
+++ b/faker/marketing_campaigns.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-08-05 11:30:01</t>
+          <t>2025-08-05 21:52:37</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-01-09 01:31:03</t>
+          <t>2026-01-09 11:53:39</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2025-07-22 19:55:40</t>
+          <t>2025-07-23 06:18:16</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>2025-10-08 11:42:58</t>
+          <t>2025-10-08 22:05:34</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>2025-01-29 19:56:53</t>
+          <t>2025-01-30 06:19:29</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>2025-04-02 15:29:43</t>
+          <t>2025-04-03 01:52:19</t>
         </is>
       </c>
     </row>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>2025-10-28 04:38:04</t>
+          <t>2025-10-28 15:00:40</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>2025-07-17 06:35:44</t>
+          <t>2025-07-17 16:58:20</t>
         </is>
       </c>
     </row>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>2025-01-13 22:23:48</t>
+          <t>2025-01-14 08:46:24</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23055,7 @@
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>2026-01-05 13:41:46</t>
+          <t>2026-01-06 00:04:22</t>
         </is>
       </c>
     </row>
@@ -23831,7 +23831,7 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2025-03-31 20:51:45  </t>
+          <t xml:space="preserve">  2025-04-01 07:14:21  </t>
         </is>
       </c>
     </row>
@@ -25155,7 +25155,7 @@
       </c>
       <c r="T321" t="inlineStr">
         <is>
-          <t>2025-03-08 16:01:28</t>
+          <t>2025-03-09 02:24:04</t>
         </is>
       </c>
     </row>
@@ -35818,7 +35818,7 @@
       </c>
       <c r="T460" t="inlineStr">
         <is>
-          <t>2025-07-18 01:55:40</t>
+          <t>2025-07-18 12:18:16</t>
         </is>
       </c>
     </row>
